--- a/docs/Final_Project/Final_Presentation.xlsx
+++ b/docs/Final_Project/Final_Presentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ConwayTeaching\GIS_I\GIS_I\docs\Final_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164C7164-B136-4B42-A4F2-E24FAF5802D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C62BB8-55CD-4E3B-A39E-B5B8FFE11020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,57 +25,97 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>Presenter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mollie, Cade, Logan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Andrew</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>William, Addie</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Becca, Krista</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Raynee, Natalie, Frankie</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Christy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lauren</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sawyer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tiffanie</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Marshall</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Eden</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Brett</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t>1. Christy</t>
+  </si>
+  <si>
+    <t>3. Brett</t>
+  </si>
+  <si>
+    <t>2. Becca, Krista</t>
+  </si>
+  <si>
+    <t>4. Andrew</t>
+  </si>
+  <si>
+    <t>5. Mollie, Cade, Logan</t>
+  </si>
+  <si>
+    <t>6. Eden</t>
+  </si>
+  <si>
+    <t>7. Raynee, Natalie, Frankie</t>
+  </si>
+  <si>
+    <t>8. Marshall</t>
+  </si>
+  <si>
+    <t>9. William, Addie</t>
+  </si>
+  <si>
+    <t>10. Tiffanie</t>
+  </si>
+  <si>
+    <t>11. Lauren</t>
+  </si>
+  <si>
+    <t>12. Sawyer</t>
+  </si>
+  <si>
+    <t>11:00-11:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:10-11:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:20-11:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:30-11:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:40-11:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:50-12:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12:00-12:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12:10-12:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12:20-12:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12:30-12:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12:40-12:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:50-11:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Final Presentation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Time- Tuesday</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -119,8 +159,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,75 +442,115 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="31.375" customWidth="1"/>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>12</v>
+      <c r="B13" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Final_Project/Final_Presentation.xlsx
+++ b/docs/Final_Project/Final_Presentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ConwayTeaching\GIS_I\GIS_I\docs\Final_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C62BB8-55CD-4E3B-A39E-B5B8FFE11020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1F0E7C-1D0E-4201-B980-9E18D214348E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -107,15 +107,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10:50-11:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Final Presentation</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Time- Tuesday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12:50 - 1:00</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -159,9 +159,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -451,18 +450,18 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
+      <c r="B2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -470,7 +469,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -478,7 +477,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -486,7 +485,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -494,7 +493,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -502,7 +501,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -510,7 +509,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -518,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -526,7 +525,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -534,7 +533,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -542,7 +541,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -550,7 +549,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
